--- a/稼働期間.xlsx
+++ b/稼働期間.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TRYS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TRYS\Downloads\daken-heatmap-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58F24E6C-3C4B-43A7-A1FE-557D9D890181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F10C672-BA0A-40E0-B142-8EE77CA11096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{FB7DE9F1-32B2-4D7D-9293-BC7348405860}"/>
+    <workbookView xWindow="1515" yWindow="3300" windowWidth="18615" windowHeight="15255" xr2:uid="{FB7DE9F1-32B2-4D7D-9293-BC7348405860}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>18 Resort Anthem</t>
     <phoneticPr fontId="1"/>
@@ -126,6 +126,10 @@
     <rPh sb="2" eb="4">
       <t>シュウリョウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34 ZINRAI</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -513,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBF83BF3-DA8D-46FC-B908-879CB6D8E939}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.875" bestFit="1" customWidth="1"/>
@@ -552,7 +556,7 @@
         <v>40801</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C17" si="0">B4-1</f>
+        <f t="shared" ref="C3:C16" si="0">B4-1</f>
         <v>41170</v>
       </c>
     </row>
@@ -719,7 +723,17 @@
       <c r="B17" s="1">
         <v>45917</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46281</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
